--- a/output/laminas_comunales/comunal_o_ocup_a_2020_aysen.xlsx
+++ b/output/laminas_comunales/comunal_o_ocup_a_2020_aysen.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C85"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -375,151 +375,1261 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>11201</t>
+          <t>11302</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="C2">
-        <v>38.6132420630237</v>
+        <v>58.1587184872267</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>11101</t>
+          <t>11201</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Coyhaique</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="C3">
-        <v>38.4686412387243</v>
+        <v>57.1687938649974</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>11302</t>
+          <t>11101</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Coyhaique</t>
         </is>
       </c>
       <c r="C4">
-        <v>38.3053221288515</v>
+        <v>56.6694567479278</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>11202</t>
+          <t>11201</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cisnes</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="C5">
-        <v>32.3956759270022</v>
+        <v>54.8013245033113</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>11102</t>
+          <t>11302</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Lago Verde</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="C6">
-        <v>32.089552238806</v>
+        <v>51.8518518518518</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>11301</t>
+          <t>11302</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cochrane</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="C7">
-        <v>31.1965099477604</v>
+        <v>49.166203617141</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>11203</t>
+          <t>11101</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Guaitecas</t>
+          <t>Coyhaique</t>
         </is>
       </c>
       <c r="C8">
-        <v>29.609500805153</v>
+        <v>49.1536027084713</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>11401</t>
+          <t>11301</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Chile Chico</t>
+          <t>Cochrane</t>
         </is>
       </c>
       <c r="C9">
-        <v>28.0110786735534</v>
+        <v>48.2893998878295</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>11303</t>
+          <t>11102</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tortel</t>
+          <t>Lago Verde</t>
         </is>
       </c>
       <c r="C10">
-        <v>26.6114180478821</v>
+        <v>47.9495268138801</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>11202</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Cisnes</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>47.6913730255164</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>11201</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>46.8184384444223</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>11302</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>46.620767716452</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>11201</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>45.7522298329473</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>11401</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Chile Chico</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>45.7097836986105</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>11102</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Lago Verde</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>45.3333333333333</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>11201</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>43.770742525044</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>11302</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>41.0514541387025</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>11203</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Guaitecas</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>40.8108108108108</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>11402</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Río Ibáñez</t>
         </is>
       </c>
-      <c r="C11">
+      <c r="C20">
+        <v>40.629117259552</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>11101</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Coyhaique</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>40.001172640234</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>11302</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>39.550343111166</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>11201</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>39.4310480512832</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>11201</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>38.6132420630237</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>11101</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Coyhaique</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>38.4686412387243</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>11302</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>38.3053221288515</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>11202</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Cisnes</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>38.2868586110481</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>11302</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>38.1818181818182</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>11101</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Coyhaique</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>36.9942330791641</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>11201</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>36.9838903979252</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>11202</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Cisnes</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>36.6923891662884</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>11302</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>35.8745874587459</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>11303</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Tortel</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>35.7142857142857</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>11301</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Cochrane</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>35.7016210739615</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>11302</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>34.2846592973778</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>11102</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Lago Verde</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>34.2836257309941</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>11201</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>34.2043352445867</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>11401</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Chile Chico</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>34.0953307392996</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>11201</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>33.1485982822881</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>11202</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Cisnes</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>32.3956759270022</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>11302</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>32.3490813648294</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>11102</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Lago Verde</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>32.089552238806</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>11203</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Guaitecas</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>31.973898858075</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>11201</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>31.4876307487963</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>11301</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Cochrane</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>31.4869603331142</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>11302</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>31.4726684981917</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>11301</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Cochrane</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>31.1965099477604</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>11301</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Cochrane</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>30.8976093820478</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>11203</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Guaitecas</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>30.4769191532772</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>11401</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Chile Chico</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>30.1565080048819</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>11203</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Guaitecas</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>29.609500805153</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>11102</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Lago Verde</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>29.5415959252971</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>11201</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>29.0717161601504</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>11101</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Coyhaique</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>29.0439001301621</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>11303</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Tortel</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>28.9893617021277</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>11203</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Guaitecas</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>28.6462758425375</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>11401</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Chile Chico</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>28.0110786735534</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>11402</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Río Ibáñez</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>27.581567440296</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>11303</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Tortel</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>27.5401069518717</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>11202</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Cisnes</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>27.3644388398487</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>11303</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Tortel</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>26.6114180478821</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>11402</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Río Ibáñez</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>26.340863685262</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>11202</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Cisnes</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>26.1967239185751</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>11301</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Cochrane</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>26.12968591692</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>11203</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Guaitecas</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>25.8200354609929</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>11401</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Chile Chico</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>25.6744076941121</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>11303</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Tortel</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>25.6190476190476</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>11401</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Chile Chico</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>24.960986267166</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>11303</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Tortel</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>24.7496423462089</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>11102</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Lago Verde</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>24.1474147414741</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>11402</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Río Ibáñez</t>
+        </is>
+      </c>
+      <c r="C71">
         <v>23.2549019607843</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>11402</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Río Ibáñez</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>22.6178700956149</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>11402</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Río Ibáñez</t>
+        </is>
+      </c>
+      <c r="C73">
+        <v>20.038443056223</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>11302</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="C74">
+        <v>19.8051948051948</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>11102</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Lago Verde</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>13.4088762983947</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>11101</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Coyhaique</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>12.3297491039427</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>11203</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Guaitecas</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>11.4335971855761</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>11302</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>11.335789167921</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>11201</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>11.1618931545805</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>11201</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>10.4498183185065</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>11202</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Cisnes</t>
+        </is>
+      </c>
+      <c r="C81">
+        <v>9.67568728522337</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>11301</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Cochrane</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>8.811802232854861</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>11401</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Chile Chico</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>8.246055020248569</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>11303</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Tortel</t>
+        </is>
+      </c>
+      <c r="C84">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>11402</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Río Ibáñez</t>
+        </is>
+      </c>
+      <c r="C85">
+        <v>6.0814455231931</v>
       </c>
     </row>
   </sheetData>
